--- a/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx
+++ b/outputs/candidates/baseline/candidate_03_vehicle_preservation.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="265">
   <si>
     <t>candidate_id</t>
   </si>
@@ -490,25 +490,25 @@
     <t>2203</t>
   </si>
   <si>
+    <t>2202</t>
+  </si>
+  <si>
     <t>2166</t>
   </si>
   <si>
     <t>353</t>
   </si>
   <si>
+    <t>2304</t>
+  </si>
+  <si>
     <t>2301</t>
   </si>
   <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
     <t>2163</t>
   </si>
   <si>
-    <t>7017</t>
+    <t>7011</t>
   </si>
   <si>
     <t>2169</t>
@@ -520,34 +520,28 @@
     <t>3013</t>
   </si>
   <si>
+    <t>7020</t>
+  </si>
+  <si>
+    <t>2161</t>
+  </si>
+  <si>
     <t>7012</t>
   </si>
   <si>
-    <t>2165</t>
-  </si>
-  <si>
-    <t>7011</t>
-  </si>
-  <si>
-    <t>7018</t>
-  </si>
-  <si>
     <t>7019</t>
   </si>
   <si>
-    <t>7020</t>
-  </si>
-  <si>
-    <t>DRV_001</t>
+    <t>DRV_007</t>
+  </si>
+  <si>
+    <t>DRV_019</t>
   </si>
   <si>
     <t>DRV_005</t>
   </si>
   <si>
-    <t>DRV_019</t>
-  </si>
-  <si>
-    <t>DRV_008</t>
+    <t>DRV_016</t>
   </si>
   <si>
     <t>DRV_017</t>
@@ -556,52 +550,46 @@
     <t>DRV_018</t>
   </si>
   <si>
+    <t>DRV_023</t>
+  </si>
+  <si>
+    <t>DRV_011</t>
+  </si>
+  <si>
+    <t>DRV_029</t>
+  </si>
+  <si>
     <t>DRV_027</t>
   </si>
   <si>
     <t>DRV_026</t>
   </si>
   <si>
+    <t>DRV_015</t>
+  </si>
+  <si>
     <t>DRV_020</t>
   </si>
   <si>
     <t>DRV_014</t>
   </si>
   <si>
-    <t>DRV_029</t>
-  </si>
-  <si>
-    <t>DRV_016</t>
-  </si>
-  <si>
-    <t>DRV_022</t>
-  </si>
-  <si>
-    <t>DRV_023</t>
-  </si>
-  <si>
-    <t>DRV_015</t>
-  </si>
-  <si>
-    <t>DRV_011</t>
-  </si>
-  <si>
     <t>DRV_009</t>
   </si>
   <si>
-    <t>박빈정</t>
+    <t>오택현</t>
   </si>
   <si>
     <t>Other 직접운전</t>
   </si>
   <si>
+    <t>황수현</t>
+  </si>
+  <si>
     <t>문하인</t>
   </si>
   <si>
-    <t>황수현</t>
-  </si>
-  <si>
-    <t>권승준</t>
+    <t>노호은</t>
   </si>
   <si>
     <t>박서민</t>
@@ -610,34 +598,28 @@
     <t>박영준</t>
   </si>
   <si>
+    <t>정수지</t>
+  </si>
+  <si>
+    <t>원허</t>
+  </si>
+  <si>
+    <t>박훈지</t>
+  </si>
+  <si>
     <t>이섭민</t>
   </si>
   <si>
     <t>제윤정</t>
   </si>
   <si>
+    <t>이준승</t>
+  </si>
+  <si>
     <t>김진무</t>
   </si>
   <si>
     <t>신훈채</t>
-  </si>
-  <si>
-    <t>박훈지</t>
-  </si>
-  <si>
-    <t>노호은</t>
-  </si>
-  <si>
-    <t>오준원</t>
-  </si>
-  <si>
-    <t>정수지</t>
-  </si>
-  <si>
-    <t>이준승</t>
-  </si>
-  <si>
-    <t>원허</t>
   </si>
   <si>
     <t>김원승</t>
@@ -1344,10 +1326,10 @@
         <v>153</v>
       </c>
       <c r="U2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="W2">
         <v>78</v>
@@ -1359,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -1427,7 +1409,7 @@
         <v>154</v>
       </c>
       <c r="V3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W3">
         <v>70</v>
@@ -1442,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1507,7 +1489,7 @@
         <v>155</v>
       </c>
       <c r="V4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W4">
         <v>70</v>
@@ -1522,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1587,7 +1569,7 @@
         <v>156</v>
       </c>
       <c r="V5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W5">
         <v>70</v>
@@ -1602,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="AD5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -1661,13 +1643,13 @@
         <v>152</v>
       </c>
       <c r="S6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W6">
         <v>70</v>
@@ -1676,13 +1658,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AD6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1741,13 +1723,13 @@
         <v>152</v>
       </c>
       <c r="S7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="V7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="W7">
         <v>70</v>
@@ -1762,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1821,16 +1803,16 @@
         <v>151</v>
       </c>
       <c r="S8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W8">
         <v>70</v>
@@ -1845,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="AD8" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1904,16 +1886,16 @@
         <v>151</v>
       </c>
       <c r="S9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="V9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W9">
         <v>70</v>
@@ -1922,13 +1904,13 @@
         <v>85</v>
       </c>
       <c r="Y9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1987,16 +1969,16 @@
         <v>151</v>
       </c>
       <c r="S10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="T10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="U10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W10">
         <v>70</v>
@@ -2011,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -2070,16 +2052,16 @@
         <v>151</v>
       </c>
       <c r="S11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="T11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="U11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="V11" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="W11">
         <v>70</v>
@@ -2094,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -2159,10 +2141,10 @@
         <v>161</v>
       </c>
       <c r="U12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="W12">
         <v>70</v>
@@ -2171,13 +2153,13 @@
         <v>85</v>
       </c>
       <c r="Y12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AD12" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -2236,16 +2218,16 @@
         <v>151</v>
       </c>
       <c r="S13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U13" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="V13" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="W13">
         <v>70</v>
@@ -2260,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AD13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -2319,16 +2301,16 @@
         <v>151</v>
       </c>
       <c r="S14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="T14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="U14" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="V14" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="W14">
         <v>70</v>
@@ -2343,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -2408,10 +2390,10 @@
         <v>162</v>
       </c>
       <c r="U15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="V15" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="W15">
         <v>70</v>
@@ -2426,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -2491,10 +2473,10 @@
         <v>163</v>
       </c>
       <c r="U16" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="V16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="W16">
         <v>70</v>
@@ -2503,13 +2485,13 @@
         <v>85</v>
       </c>
       <c r="Y16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
       <c r="AD16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -2574,10 +2556,10 @@
         <v>162</v>
       </c>
       <c r="U17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="V17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="W17">
         <v>70</v>
@@ -2592,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="AD17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:30">
@@ -2657,10 +2639,10 @@
         <v>164</v>
       </c>
       <c r="U18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="V18" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="W18">
         <v>70</v>
@@ -2675,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -2740,10 +2722,10 @@
         <v>165</v>
       </c>
       <c r="U19" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="V19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="W19">
         <v>70</v>
@@ -2758,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="AD19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:30">
@@ -2823,10 +2805,10 @@
         <v>166</v>
       </c>
       <c r="U20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W20">
         <v>70</v>
@@ -2841,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -2906,10 +2888,10 @@
         <v>166</v>
       </c>
       <c r="U21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="V21" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="W21">
         <v>70</v>
@@ -2924,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -2989,10 +2971,10 @@
         <v>167</v>
       </c>
       <c r="U22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="V22" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="W22">
         <v>75</v>
@@ -3007,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AD22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -3072,10 +3054,10 @@
         <v>168</v>
       </c>
       <c r="U23" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="V23" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="W23">
         <v>70</v>
@@ -3084,13 +3066,13 @@
         <v>85</v>
       </c>
       <c r="Y23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AD23" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -3149,13 +3131,13 @@
         <v>151</v>
       </c>
       <c r="S24" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="T24" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="U24" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="V24" t="s">
         <v>200</v>
@@ -3173,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="AD24" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -3238,10 +3220,10 @@
         <v>169</v>
       </c>
       <c r="U25" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="V25" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="W25">
         <v>75</v>
@@ -3256,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="AD25" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -3315,16 +3297,16 @@
         <v>151</v>
       </c>
       <c r="S26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="T26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="V26" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="W26">
         <v>75</v>
@@ -3339,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AD26" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:30">
@@ -3398,16 +3380,16 @@
         <v>151</v>
       </c>
       <c r="S27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="T27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="U27" t="s">
         <v>182</v>
       </c>
       <c r="V27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="W27">
         <v>75</v>
@@ -3422,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="AD27" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:30">
@@ -3481,16 +3463,16 @@
         <v>151</v>
       </c>
       <c r="S28" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="T28" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="U28" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="V28" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="W28">
         <v>75</v>
@@ -3505,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="AD28" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -3564,16 +3546,16 @@
         <v>151</v>
       </c>
       <c r="S29" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="T29" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="U29" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="V29" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="W29">
         <v>75</v>
@@ -3588,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="AD29" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:30">
@@ -3647,16 +3629,16 @@
         <v>151</v>
       </c>
       <c r="S30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="T30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="U30" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V30" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="W30">
         <v>75</v>
@@ -3671,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:30">
@@ -3730,16 +3712,16 @@
         <v>151</v>
       </c>
       <c r="S31" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="T31" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="U31" t="s">
         <v>182</v>
       </c>
       <c r="V31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="W31">
         <v>75</v>
@@ -3748,13 +3730,13 @@
         <v>85</v>
       </c>
       <c r="Y31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
       </c>
       <c r="AD31" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:30">
@@ -3813,16 +3795,16 @@
         <v>151</v>
       </c>
       <c r="S32" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="T32" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="U32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="V32" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="W32">
         <v>75</v>
@@ -3837,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -3896,16 +3878,16 @@
         <v>151</v>
       </c>
       <c r="S33" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="T33" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="U33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V33" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="W33">
         <v>75</v>
@@ -3920,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AD33" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:30">
@@ -3979,16 +3961,16 @@
         <v>151</v>
       </c>
       <c r="S34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="T34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="U34" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="V34" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="W34">
         <v>75</v>
@@ -4003,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="AD34" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:30">
@@ -4068,10 +4050,10 @@
         <v>164</v>
       </c>
       <c r="U35" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="V35" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="W35">
         <v>70</v>
@@ -4086,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="AD35" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4107,61 +4089,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -4172,10 +4154,10 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E2">
         <v>14855</v>
@@ -4217,13 +4199,13 @@
         <v>10</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T2">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="U2">
         <v>34</v>
@@ -4250,209 +4232,209 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" t="s">
         <v>253</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
         <v>259</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B11" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
